--- a/output.xlsx
+++ b/output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3225B48-D499-4DE0-81BE-F9A9A04DBF18}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D494672D-2C15-4AC0-AC38-F1225824DEF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,12 @@
     <sheet name="ზუკა" sheetId="6" r:id="rId6"/>
     <sheet name="ირმა" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="39">
   <si>
     <t>Bank</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>ცელერისი შემოსავალი</t>
+  </si>
+  <si>
+    <t>არ მომწერა კოდი</t>
   </si>
 </sst>
 </file>
@@ -148,7 +151,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -192,7 +195,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,6 +226,24 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -237,15 +258,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -550,7 +575,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -558,7 +583,7 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -586,7 +611,7 @@
         <v>1937.16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -600,7 +625,7 @@
         <v>970.3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -614,7 +639,7 @@
         <v>850.27</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -628,7 +653,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -640,7 +665,7 @@
         <v>3957.73</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -654,7 +679,7 @@
         <v>6850.67</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -668,7 +693,7 @@
         <v>6123.55</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -682,7 +707,7 @@
         <v>4185.6099999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -696,7 +721,7 @@
         <v>4067.52</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -710,7 +735,7 @@
         <v>3712.89</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -724,7 +749,7 @@
         <v>3456.21</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -738,7 +763,7 @@
         <v>3330.21</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -752,7 +777,7 @@
         <v>3305.06</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -766,7 +791,7 @@
         <v>2962.01</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -780,7 +805,7 @@
         <v>992.53</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -794,7 +819,7 @@
         <v>560.46</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>21</v>
@@ -806,7 +831,7 @@
         <v>39546.720000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -820,7 +845,7 @@
         <v>3740.44</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -834,7 +859,7 @@
         <v>1368.47</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -848,7 +873,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
@@ -862,7 +887,7 @@
         <v>1267.17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
@@ -876,7 +901,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>23</v>
@@ -901,8 +926,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -910,7 +935,7 @@
     <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -924,25 +949,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="8">
         <v>8176.67</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2">
@@ -951,54 +976,57 @@
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="8">
         <v>6123.55</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="D4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>5534.6900000000014</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>4826.8899999999994</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="2">
@@ -1007,64 +1035,67 @@
       <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="8">
         <v>4306.4799999999996</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>4185.6099999999997</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="D9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="8">
         <v>3305.06</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="D10" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="8">
         <v>2962.01</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D11" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
@@ -1078,21 +1109,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="8">
         <v>560.46</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D13" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>28</v>
@@ -1104,13 +1135,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -1119,7 +1151,7 @@
     <col min="5" max="5" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1136,7 +1168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>46143</v>
       </c>
@@ -1157,7 +1189,7 @@
         <v>318.87755102040813</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>46156</v>
       </c>
@@ -1178,7 +1210,7 @@
         <v>1275.5102040816325</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>46164</v>
       </c>
@@ -1199,7 +1231,7 @@
         <v>286.98979591836735</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>46170</v>
       </c>
@@ -1220,7 +1252,7 @@
         <v>1530.6122448979593</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>46170</v>
       </c>
@@ -1241,7 +1273,7 @@
         <v>1275.5102040816325</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>46171</v>
       </c>
@@ -1262,7 +1294,7 @@
         <v>286.98979591836735</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>46146</v>
       </c>
@@ -1283,7 +1315,7 @@
         <v>382.65306122448982</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>46153</v>
       </c>
@@ -1304,7 +1336,7 @@
         <v>382.65306122448982</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>46160</v>
       </c>
@@ -1325,7 +1357,7 @@
         <v>382.65306122448982</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>46167</v>
       </c>
@@ -1346,7 +1378,7 @@
         <v>127.55102040816327</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
@@ -1361,7 +1393,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1377,7 +1409,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1385,7 +1417,7 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1399,7 +1431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1413,7 +1445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1427,7 +1459,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -1441,7 +1473,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -1455,7 +1487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1469,7 +1501,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -1483,7 +1515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1497,7 +1529,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1511,7 +1543,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1525,7 +1557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1539,7 +1571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
@@ -1553,7 +1585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1567,7 +1599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>34</v>
@@ -1585,7 +1617,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1593,7 +1625,7 @@
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1621,7 +1653,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1635,7 +1667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1649,7 +1681,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1663,7 +1695,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1677,7 +1709,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>34</v>
@@ -1695,7 +1727,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -1703,7 +1735,7 @@
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1717,27 +1749,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="10">
         <v>1132.5</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1034.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5">
         <f>SUM(C3:C4)</f>
         <v>1132.5</v>
@@ -1755,7 +1787,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -1763,7 +1795,7 @@
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1777,27 +1809,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="10">
         <v>4872.4699999999993</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>2456.1999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>2416.27</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5">
         <f>C3+C4</f>
         <v>4872.4699999999993</v>

--- a/output.xlsx
+++ b/output.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D494672D-2C15-4AC0-AC38-F1225824DEF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6167C6E-AD17-47CB-A5F6-1D073B71016A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
-    <sheet name="Salary" sheetId="3" r:id="rId3"/>
-    <sheet name="მომსახ დელ" sheetId="4" r:id="rId4"/>
-    <sheet name="მომსახ ცელ" sheetId="5" r:id="rId5"/>
-    <sheet name="ზუკა" sheetId="6" r:id="rId6"/>
-    <sheet name="ირმა" sheetId="7" r:id="rId7"/>
+    <sheet name="დელივერერები 1%" sheetId="8" r:id="rId3"/>
+    <sheet name="Salary" sheetId="3" r:id="rId4"/>
+    <sheet name="მომსახ დელ" sheetId="4" r:id="rId5"/>
+    <sheet name="მომსახ ცელ" sheetId="5" r:id="rId6"/>
+    <sheet name="ზუკა" sheetId="6" r:id="rId7"/>
+    <sheet name="ირმა" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="39">
   <si>
     <t>Bank</t>
   </si>
@@ -153,7 +154,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +194,12 @@
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -258,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -271,6 +278,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -926,7 +936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -935,7 +945,7 @@
     <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -949,7 +959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
@@ -962,8 +972,12 @@
       <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="12">
+        <f>C2*0.01</f>
+        <v>81.7667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -979,8 +993,12 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="12">
+        <f t="shared" ref="F3:F13" si="0">C3*0.01</f>
+        <v>66.358400000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
@@ -993,8 +1011,12 @@
       <c r="D4" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="12">
+        <f t="shared" si="0"/>
+        <v>61.235500000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
@@ -1007,8 +1029,12 @@
       <c r="D5" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="12">
+        <f t="shared" si="0"/>
+        <v>55.346900000000012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
@@ -1021,8 +1047,12 @@
       <c r="D6" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="12">
+        <f t="shared" si="0"/>
+        <v>48.268899999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -1038,8 +1068,12 @@
       <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="12">
+        <f t="shared" si="0"/>
+        <v>47.329700000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>25</v>
       </c>
@@ -1052,8 +1086,12 @@
       <c r="D8" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="12">
+        <f t="shared" si="0"/>
+        <v>43.064799999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
@@ -1066,8 +1104,12 @@
       <c r="D9" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="12">
+        <f t="shared" si="0"/>
+        <v>41.856099999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1122,12 @@
       <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>33.050600000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>11</v>
       </c>
@@ -1094,8 +1140,12 @@
       <c r="D11" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="12">
+        <f t="shared" si="0"/>
+        <v>29.620100000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
@@ -1108,8 +1158,12 @@
       <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="12">
+        <f t="shared" si="0"/>
+        <v>9.7029999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
@@ -1122,8 +1176,12 @@
       <c r="D13" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="12">
+        <f t="shared" si="0"/>
+        <v>5.6046000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>28</v>
@@ -1140,6 +1198,116 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954EBA50-267C-45AD-A357-6C9100E13950}">
+  <dimension ref="B3:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="14">
+        <v>81.7667</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="14">
+        <v>66.358400000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="14">
+        <v>61.235500000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="14">
+        <v>55.346900000000012</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="14">
+        <v>48.268899999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="14">
+        <v>47.329700000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="14">
+        <v>43.064799999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="14">
+        <v>41.856099999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="14">
+        <v>33.050600000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="14">
+        <v>29.620100000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="14">
+        <v>9.7029999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="14">
+        <v>5.6046000000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1406,7 +1574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1614,7 +1782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1724,7 +1892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1784,7 +1952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/output.xlsx
+++ b/output.xlsx
@@ -8,26 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6167C6E-AD17-47CB-A5F6-1D073B71016A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E19EFD-288C-41EE-818A-FB411005EFD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
-    <sheet name="დელივერერები 1%" sheetId="8" r:id="rId3"/>
-    <sheet name="Salary" sheetId="3" r:id="rId4"/>
-    <sheet name="მომსახ დელ" sheetId="4" r:id="rId5"/>
-    <sheet name="მომსახ ცელ" sheetId="5" r:id="rId6"/>
-    <sheet name="ზუკა" sheetId="6" r:id="rId7"/>
-    <sheet name="ირმა" sheetId="7" r:id="rId8"/>
+    <sheet name="Salary" sheetId="3" r:id="rId3"/>
+    <sheet name="მომსახ დელ" sheetId="4" r:id="rId4"/>
+    <sheet name="მომსახ ცელ" sheetId="5" r:id="rId5"/>
+    <sheet name="ზუკა" sheetId="6" r:id="rId6"/>
+    <sheet name="ირმა" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="39">
   <si>
     <t>Bank</t>
   </si>
@@ -154,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,12 +193,6 @@
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -265,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -279,8 +272,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1198,116 +1189,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954EBA50-267C-45AD-A357-6C9100E13950}">
-  <dimension ref="B3:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="14">
-        <v>81.7667</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="14">
-        <v>66.358400000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="14">
-        <v>61.235500000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="14">
-        <v>55.346900000000012</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="14">
-        <v>48.268899999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="14">
-        <v>47.329700000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="14">
-        <v>43.064799999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="14">
-        <v>41.856099999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="14">
-        <v>33.050600000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="14">
-        <v>29.620100000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="14">
-        <v>9.7029999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="14">
-        <v>5.6046000000000005</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1574,7 +1455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1782,7 +1663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1892,7 +1773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1952,7 +1833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
